--- a/3_CGE/Game_theory_2024/5_Visualisation/QOE_Eq_Brazil_Detailed_Results.xlsx
+++ b/3_CGE/Game_theory_2024/5_Visualisation/QOE_Eq_Brazil_Detailed_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\runGTAP375\Game_theory_2024\5_Visualisation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78B6F05-50A6-47E1-80F8-3D972518F23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478976EC-7528-42BB-90C8-05A6B7F2DFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27440" yWindow="-21810" windowWidth="38620" windowHeight="21100" xr2:uid="{DC9D0EDD-2438-42C5-B34B-D056689AD448}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{DC9D0EDD-2438-42C5-B34B-D056689AD448}"/>
   </bookViews>
   <sheets>
     <sheet name="p_HARVSTAREA_L" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="61">
   <si>
     <t>p_HARVSTAREA_L</t>
   </si>
@@ -159,6 +159,72 @@
   </si>
   <si>
     <t>Forest</t>
+  </si>
+  <si>
+    <t>1 AEZ1</t>
+  </si>
+  <si>
+    <t>2 AEZ2</t>
+  </si>
+  <si>
+    <t>3 AEZ3</t>
+  </si>
+  <si>
+    <t>4 AEZ4</t>
+  </si>
+  <si>
+    <t>5 AEZ5</t>
+  </si>
+  <si>
+    <t>6 AEZ6</t>
+  </si>
+  <si>
+    <t>7 AEZ7</t>
+  </si>
+  <si>
+    <t>8 AEZ8</t>
+  </si>
+  <si>
+    <t>9 AEZ9</t>
+  </si>
+  <si>
+    <t>10 AEZ10</t>
+  </si>
+  <si>
+    <t>11 AEZ11</t>
+  </si>
+  <si>
+    <t>12 AEZ12</t>
+  </si>
+  <si>
+    <t>13 AEZ13</t>
+  </si>
+  <si>
+    <t>14 AEZ14</t>
+  </si>
+  <si>
+    <t>15 AEZ15</t>
+  </si>
+  <si>
+    <t>16 AEZ16</t>
+  </si>
+  <si>
+    <t>17 AEZ17</t>
+  </si>
+  <si>
+    <t>18 AEZ18</t>
+  </si>
+  <si>
+    <t>1 Forestland</t>
+  </si>
+  <si>
+    <t>2 SavnGrasland</t>
+  </si>
+  <si>
+    <t>5 Pastureland</t>
+  </si>
+  <si>
+    <t>del_LUC[**Brasil]</t>
   </si>
 </sst>
 </file>
@@ -567,28 +633,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -596,28 +662,28 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -625,28 +691,28 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -654,28 +720,28 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -683,28 +749,28 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -712,28 +778,28 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -741,28 +807,28 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>5.6517090000000003</v>
+        <v>8.0404999999999998</v>
       </c>
       <c r="C8">
-        <v>-4.2775189999999998</v>
+        <v>-5.8598999999999997</v>
       </c>
       <c r="D8">
-        <v>-1.744013</v>
+        <v>-2.6132</v>
       </c>
       <c r="E8">
-        <v>-7.0331000000000005E-2</v>
+        <v>-0.45069999999999999</v>
       </c>
       <c r="F8">
-        <v>-3.200844</v>
+        <v>-4.4812000000000003</v>
       </c>
       <c r="G8">
-        <v>12.666216</v>
+        <v>20.015599999999999</v>
       </c>
       <c r="H8">
-        <v>-3.2666149999999998</v>
+        <v>-4.5829000000000004</v>
       </c>
       <c r="I8">
-        <v>0.33206599999999997</v>
+        <v>6.7299999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -770,28 +836,28 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>7.9349049999999997</v>
+        <v>-2.7046999999999999</v>
       </c>
       <c r="C9">
-        <v>3.9254380000000002</v>
+        <v>-1.3637999999999999</v>
       </c>
       <c r="D9">
-        <v>2.5640480000000001</v>
+        <v>-0.42959999999999998</v>
       </c>
       <c r="E9">
-        <v>7.7079029999999999</v>
+        <v>-8.6900000000000005E-2</v>
       </c>
       <c r="F9">
-        <v>-1.8586210000000001</v>
+        <v>-0.79379999999999995</v>
       </c>
       <c r="G9">
-        <v>15.101006999999999</v>
+        <v>8.0793999999999997</v>
       </c>
       <c r="H9">
-        <v>-4.5003890000000002</v>
+        <v>-0.80669999999999997</v>
       </c>
       <c r="I9">
-        <v>-4.9280299999999997</v>
+        <v>4.1099999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -799,28 +865,28 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>7.1509020000000003</v>
+        <v>2.4563999999999999</v>
       </c>
       <c r="C10">
-        <v>3.170569</v>
+        <v>3.4664999999999999</v>
       </c>
       <c r="D10">
-        <v>1.819051</v>
+        <v>0.33950000000000002</v>
       </c>
       <c r="E10">
-        <v>6.9255500000000003</v>
+        <v>5.8</v>
       </c>
       <c r="F10">
-        <v>-2.5714779999999999</v>
+        <v>-6.9187000000000003</v>
       </c>
       <c r="G10">
-        <v>14.264945000000001</v>
+        <v>13.8126</v>
       </c>
       <c r="H10">
-        <v>-5.1940650000000002</v>
+        <v>-9.5023999999999997</v>
       </c>
       <c r="I10">
-        <v>-5.6186100000000003</v>
+        <v>-5.0252999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -828,28 +894,28 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -857,28 +923,28 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -886,28 +952,28 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>4.6203479999999999</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0.73415699999999995</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>-0.585565</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>4.400328</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>-4.8713629999999997</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>11.566395</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>-7.433052</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>-7.8475849999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -915,28 +981,28 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>-14.177246999999999</v>
+        <v>-21.9345</v>
       </c>
       <c r="C14">
-        <v>-3.4982329999999999</v>
+        <v>-3.4681999999999999</v>
       </c>
       <c r="D14">
-        <v>-2.8815680000000001</v>
+        <v>-3.0270000000000001</v>
       </c>
       <c r="E14">
-        <v>-1.3863540000000001</v>
+        <v>-1.9481999999999999</v>
       </c>
       <c r="F14">
-        <v>-3.1731850000000001</v>
+        <v>-3.2658999999999998</v>
       </c>
       <c r="G14">
-        <v>-8.4792459999999998</v>
+        <v>-13.2818</v>
       </c>
       <c r="H14">
-        <v>-5.0663289999999996</v>
+        <v>-4.8281999999999998</v>
       </c>
       <c r="I14">
-        <v>-1.1696569999999999</v>
+        <v>-1.7769999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -944,28 +1010,28 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>0.25600099999999998</v>
+        <v>-2.9226999999999999</v>
       </c>
       <c r="C15">
-        <v>-6.1767909999999997</v>
+        <v>-10.9975</v>
       </c>
       <c r="D15">
-        <v>-4.1274389999999999</v>
+        <v>-7.2374999999999998</v>
       </c>
       <c r="E15">
-        <v>-0.30588100000000001</v>
+        <v>-0.41870000000000002</v>
       </c>
       <c r="F15">
-        <v>-5.3841939999999999</v>
+        <v>-9.5140999999999991</v>
       </c>
       <c r="G15">
-        <v>6.9122599999999998</v>
+        <v>7.8372000000000002</v>
       </c>
       <c r="H15">
-        <v>-6.3496899999999998</v>
+        <v>-10.9428</v>
       </c>
       <c r="I15">
-        <v>0.18304699999999999</v>
+        <v>0.44340000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -973,28 +1039,28 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>7.6475590000000002</v>
+        <v>-3.7888999999999999</v>
       </c>
       <c r="C16">
-        <v>-2.444493</v>
+        <v>-0.59570000000000001</v>
       </c>
       <c r="D16">
-        <v>-1.7952399999999999</v>
+        <v>-0.46510000000000001</v>
       </c>
       <c r="E16">
-        <v>-0.12923999999999999</v>
+        <v>0.13059999999999999</v>
       </c>
       <c r="F16">
-        <v>-2.334171</v>
+        <v>-0.60129999999999995</v>
       </c>
       <c r="G16">
-        <v>14.794568999999999</v>
+        <v>6.875</v>
       </c>
       <c r="H16">
-        <v>-5.3062709999999997</v>
+        <v>-1.6910000000000001</v>
       </c>
       <c r="I16">
-        <v>0.20089499999999999</v>
+        <v>0.2369</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1002,28 +1068,28 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>1.46821</v>
+        <v>-5.2941000000000003</v>
       </c>
       <c r="C17">
-        <v>-0.19665099999999999</v>
+        <v>-0.1101</v>
       </c>
       <c r="D17">
-        <v>-0.18399199999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="E17">
-        <v>-0.107263</v>
+        <v>-6.6000000000000003E-2</v>
       </c>
       <c r="F17">
-        <v>-0.42719099999999999</v>
+        <v>-0.25319999999999998</v>
       </c>
       <c r="G17">
-        <v>8.2049529999999997</v>
+        <v>5.2030000000000003</v>
       </c>
       <c r="H17">
-        <v>-1.8029660000000001</v>
+        <v>-1.1184000000000001</v>
       </c>
       <c r="I17">
-        <v>7.1809999999999999E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1031,28 +1097,28 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>4.4907069999999996</v>
+        <v>7.3517999999999999</v>
       </c>
       <c r="C18">
-        <v>0.60896499999999998</v>
+        <v>8.4100999999999999</v>
       </c>
       <c r="D18">
-        <v>-0.70878300000000005</v>
+        <v>5.1337999999999999</v>
       </c>
       <c r="E18">
-        <v>4.2709349999999997</v>
+        <v>10.8551</v>
       </c>
       <c r="F18">
-        <v>-4.9892690000000002</v>
+        <v>-2.4712999999999998</v>
       </c>
       <c r="G18">
-        <v>11.428124</v>
+        <v>19.250599999999999</v>
       </c>
       <c r="H18">
-        <v>-7.547803</v>
+        <v>-5.1783000000000001</v>
       </c>
       <c r="I18">
-        <v>-7.961786</v>
+        <v>-0.4874</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1060,28 +1126,28 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>4.6203479999999999</v>
+        <v>8.0907</v>
       </c>
       <c r="C19">
-        <v>0.73415699999999995</v>
+        <v>5.2328000000000001</v>
       </c>
       <c r="D19">
-        <v>-0.585565</v>
+        <v>5.8574000000000002</v>
       </c>
       <c r="E19">
-        <v>4.400328</v>
+        <v>11.6181</v>
       </c>
       <c r="F19">
-        <v>-4.8713629999999997</v>
+        <v>-1.8</v>
       </c>
       <c r="G19">
-        <v>11.566395</v>
+        <v>20.071400000000001</v>
       </c>
       <c r="H19">
-        <v>-7.433052</v>
+        <v>-4.5256999999999996</v>
       </c>
       <c r="I19">
-        <v>-7.8475849999999996</v>
+        <v>0.19750000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1323,28 +1389,28 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>51.921290999999997</v>
+        <v>52.5184</v>
       </c>
       <c r="C8">
-        <v>-88.525870999999995</v>
+        <v>-68.492699999999999</v>
       </c>
       <c r="D8">
-        <v>-102.420731</v>
+        <v>-131.39830000000001</v>
       </c>
       <c r="E8">
-        <v>-1.0759460000000001</v>
+        <v>-4.6904000000000003</v>
       </c>
       <c r="F8">
-        <v>-332.04049700000002</v>
+        <v>-434.22340000000003</v>
       </c>
       <c r="G8">
-        <v>40.565761999999999</v>
+        <v>30.169499999999999</v>
       </c>
       <c r="H8">
-        <v>-1.232755</v>
+        <v>-1.0528999999999999</v>
       </c>
       <c r="I8">
-        <v>2.1627010000000002</v>
+        <v>0.28389999999999999</v>
       </c>
       <c r="J8">
         <v>-430.64604700000001</v>
@@ -1355,28 +1421,28 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>0.61266799999999999</v>
+        <v>-0.1061</v>
       </c>
       <c r="C9">
-        <v>1.7031999999999999E-2</v>
+        <v>-9.7999999999999997E-3</v>
       </c>
       <c r="D9">
-        <v>5.6543659999999996</v>
+        <v>-0.70379999999999998</v>
       </c>
       <c r="E9">
-        <v>6.3272300000000001</v>
+        <v>-4.0300000000000002E-2</v>
       </c>
       <c r="F9">
-        <v>-0.46724100000000002</v>
+        <v>-0.1095</v>
       </c>
       <c r="G9">
-        <v>2.7011250000000002</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="H9">
-        <v>-2.1767999999999999E-2</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="I9">
-        <v>-10.761381</v>
+        <v>4.4299999999999999E-2</v>
       </c>
       <c r="J9">
         <v>4.0620310000000002</v>
@@ -1387,28 +1453,28 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>4.1939999999999998E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="C10">
-        <v>1.3181999999999999E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="D10">
-        <v>1.1394E-2</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="E10">
-        <v>0.26932200000000001</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="F10">
-        <v>-3.5279999999999999E-3</v>
+        <v>-2.5499999999999998E-2</v>
       </c>
       <c r="G10">
-        <v>0.18691199999999999</v>
+        <v>0.30819999999999997</v>
       </c>
       <c r="H10">
-        <v>-2.5724E-2</v>
+        <v>-7.6999999999999999E-2</v>
       </c>
       <c r="I10">
-        <v>-0.39590999999999998</v>
+        <v>-0.34970000000000001</v>
       </c>
       <c r="J10">
         <v>5.9841999999999999E-2</v>
@@ -1515,28 +1581,28 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>-30.199594000000001</v>
+        <v>-34.202800000000003</v>
       </c>
       <c r="C14">
-        <v>-23.643055</v>
+        <v>-29.851600000000001</v>
       </c>
       <c r="D14">
-        <v>-87.117576999999997</v>
+        <v>-145.70849999999999</v>
       </c>
       <c r="E14">
-        <v>-19.436703000000001</v>
+        <v>-23.3551</v>
       </c>
       <c r="F14">
-        <v>-153.390625</v>
+        <v>-265.97550000000001</v>
       </c>
       <c r="G14">
-        <v>-265.663116</v>
+        <v>-306.798</v>
       </c>
       <c r="H14">
-        <v>-5.141947</v>
+        <v>-7.4972000000000003</v>
       </c>
       <c r="I14">
-        <v>-11.141334000000001</v>
+        <v>-14.496600000000001</v>
       </c>
       <c r="J14">
         <v>-595.73395100000005</v>
@@ -1547,28 +1613,28 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>2.0877680000000001</v>
+        <v>-8.9189000000000007</v>
       </c>
       <c r="C15">
-        <v>-4.6764849999999996</v>
+        <v>-3.6669</v>
       </c>
       <c r="D15">
-        <v>-204.32745399999999</v>
+        <v>-250.5797</v>
       </c>
       <c r="E15">
-        <v>-7.4282320000000004</v>
+        <v>-5.8076999999999996</v>
       </c>
       <c r="F15">
-        <v>-733.12066700000003</v>
+        <v>-781.12350000000004</v>
       </c>
       <c r="G15">
-        <v>446.67910799999999</v>
+        <v>428.16919999999999</v>
       </c>
       <c r="H15">
-        <v>-51.399303000000003</v>
+        <v>-60.348999999999997</v>
       </c>
       <c r="I15">
-        <v>2.1782119999999998</v>
+        <v>4.8090000000000002</v>
       </c>
       <c r="J15">
         <v>-550.00705300000004</v>
@@ -1579,28 +1645,28 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>26.508167</v>
+        <v>-19.5181</v>
       </c>
       <c r="C16">
-        <v>-0.27185700000000002</v>
+        <v>-0.1847</v>
       </c>
       <c r="D16">
-        <v>-31.586706</v>
+        <v>-15.155099999999999</v>
       </c>
       <c r="E16">
-        <v>-2.50556</v>
+        <v>1.9624999999999999</v>
       </c>
       <c r="F16">
-        <v>-48.283478000000002</v>
+        <v>-62.6068</v>
       </c>
       <c r="G16">
-        <v>62.584885</v>
+        <v>132.86850000000001</v>
       </c>
       <c r="H16">
-        <v>-11.884573</v>
+        <v>-12.8294</v>
       </c>
       <c r="I16">
-        <v>0.33964800000000001</v>
+        <v>0.71489999999999998</v>
       </c>
       <c r="J16">
         <v>-5.099475</v>
@@ -1611,28 +1677,28 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>0.54722000000000004</v>
+        <v>-3.7031000000000001</v>
       </c>
       <c r="C17">
-        <v>-3.6250000000000002E-3</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="D17">
-        <v>-1.485584</v>
+        <v>-1.8046</v>
       </c>
       <c r="E17">
-        <v>-0.98438800000000004</v>
+        <v>-0.91890000000000005</v>
       </c>
       <c r="F17">
-        <v>-0.52605500000000005</v>
+        <v>-0.69230000000000003</v>
       </c>
       <c r="G17">
-        <v>4.6515690000000003</v>
+        <v>8.9803999999999995</v>
       </c>
       <c r="H17">
-        <v>-2.0923020000000001</v>
+        <v>-1.6872</v>
       </c>
       <c r="I17">
-        <v>1.4499999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="J17">
         <v>0.10828599999999999</v>
@@ -1643,28 +1709,28 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>8.8683999999999999E-2</v>
+        <v>0.4778</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.30330000000000001</v>
       </c>
       <c r="D18">
-        <v>-0.29504399999999997</v>
+        <v>25.370899999999999</v>
       </c>
       <c r="E18">
-        <v>2.7304270000000002</v>
+        <v>55.1586</v>
       </c>
       <c r="F18">
-        <v>-0.27462399999999998</v>
+        <v>-1.4886999999999999</v>
       </c>
       <c r="G18">
-        <v>0.60196700000000003</v>
+        <v>6.6901000000000002</v>
       </c>
       <c r="H18">
-        <v>-0.22628499999999999</v>
+        <v>-4.9657</v>
       </c>
       <c r="I18">
-        <v>-1.37E-4</v>
+        <v>-0.1744</v>
       </c>
       <c r="J18">
         <v>2.6249880000000001</v>
@@ -1675,28 +1741,28 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.56259999999999999</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2.5266999999999999</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>-7.7399999999999997E-2</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2.8614000000000002</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>-0.498</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1.5E-3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1778,35 +1844,35 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <f>Sheet2!B2*100</f>
+        <f>Sheet2!B2*1000</f>
         <v>0</v>
       </c>
       <c r="C2">
-        <f>Sheet2!C2*100</f>
+        <f>Sheet2!C2*1000</f>
         <v>0</v>
       </c>
       <c r="D2">
-        <f>Sheet2!D2*100</f>
+        <f>Sheet2!D2*1000</f>
         <v>0</v>
       </c>
       <c r="E2">
-        <f>Sheet2!E2*100</f>
+        <f>Sheet2!E2*1000</f>
         <v>0</v>
       </c>
       <c r="F2">
-        <f>Sheet2!F2*100</f>
+        <f>Sheet2!F2*1000</f>
         <v>0</v>
       </c>
       <c r="G2">
-        <f>Sheet2!G2*100</f>
+        <f>Sheet2!G2*1000</f>
         <v>0</v>
       </c>
       <c r="H2">
-        <f>Sheet2!H2*100</f>
+        <f>Sheet2!H2*1000</f>
         <v>0</v>
       </c>
       <c r="I2">
-        <f>Sheet2!I2*100</f>
+        <f>Sheet2!I2*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -1815,35 +1881,35 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <f>Sheet2!B3*100</f>
+        <f>Sheet2!B3*1000</f>
         <v>0</v>
       </c>
       <c r="C3">
-        <f>Sheet2!C3*100</f>
+        <f>Sheet2!C3*1000</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f>Sheet2!D3*100</f>
+        <f>Sheet2!D3*1000</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f>Sheet2!E3*100</f>
+        <f>Sheet2!E3*1000</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>Sheet2!F3*100</f>
+        <f>Sheet2!F3*1000</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f>Sheet2!G3*100</f>
+        <f>Sheet2!G3*1000</f>
         <v>0</v>
       </c>
       <c r="H3">
-        <f>Sheet2!H3*100</f>
+        <f>Sheet2!H3*1000</f>
         <v>0</v>
       </c>
       <c r="I3">
-        <f>Sheet2!I3*100</f>
+        <f>Sheet2!I3*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -1852,35 +1918,35 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <f>Sheet2!B4*100</f>
+        <f>Sheet2!B4*1000</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f>Sheet2!C4*100</f>
+        <f>Sheet2!C4*1000</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f>Sheet2!D4*100</f>
+        <f>Sheet2!D4*1000</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>Sheet2!E4*100</f>
+        <f>Sheet2!E4*1000</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>Sheet2!F4*100</f>
+        <f>Sheet2!F4*1000</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>Sheet2!G4*100</f>
+        <f>Sheet2!G4*1000</f>
         <v>0</v>
       </c>
       <c r="H4">
-        <f>Sheet2!H4*100</f>
+        <f>Sheet2!H4*1000</f>
         <v>0</v>
       </c>
       <c r="I4">
-        <f>Sheet2!I4*100</f>
+        <f>Sheet2!I4*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -1889,35 +1955,35 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <f>Sheet2!B5*100</f>
+        <f>Sheet2!B5*1000</f>
         <v>0</v>
       </c>
       <c r="C5">
-        <f>Sheet2!C5*100</f>
+        <f>Sheet2!C5*1000</f>
         <v>0</v>
       </c>
       <c r="D5">
-        <f>Sheet2!D5*100</f>
+        <f>Sheet2!D5*1000</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>Sheet2!E5*100</f>
+        <f>Sheet2!E5*1000</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>Sheet2!F5*100</f>
+        <f>Sheet2!F5*1000</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>Sheet2!G5*100</f>
+        <f>Sheet2!G5*1000</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>Sheet2!H5*100</f>
+        <f>Sheet2!H5*1000</f>
         <v>0</v>
       </c>
       <c r="I5">
-        <f>Sheet2!I5*100</f>
+        <f>Sheet2!I5*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -1926,35 +1992,35 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <f>Sheet2!B6*100</f>
+        <f>Sheet2!B6*1000</f>
         <v>0</v>
       </c>
       <c r="C6">
-        <f>Sheet2!C6*100</f>
+        <f>Sheet2!C6*1000</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>Sheet2!D6*100</f>
+        <f>Sheet2!D6*1000</f>
         <v>0</v>
       </c>
       <c r="E6">
-        <f>Sheet2!E6*100</f>
+        <f>Sheet2!E6*1000</f>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>Sheet2!F6*100</f>
+        <f>Sheet2!F6*1000</f>
         <v>0</v>
       </c>
       <c r="G6">
-        <f>Sheet2!G6*100</f>
+        <f>Sheet2!G6*1000</f>
         <v>0</v>
       </c>
       <c r="H6">
-        <f>Sheet2!H6*100</f>
+        <f>Sheet2!H6*1000</f>
         <v>0</v>
       </c>
       <c r="I6">
-        <f>Sheet2!I6*100</f>
+        <f>Sheet2!I6*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -1963,35 +2029,35 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <f>Sheet2!B7*100</f>
+        <f>Sheet2!B7*1000</f>
         <v>0</v>
       </c>
       <c r="C7">
-        <f>Sheet2!C7*100</f>
+        <f>Sheet2!C7*1000</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>Sheet2!D7*100</f>
+        <f>Sheet2!D7*1000</f>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>Sheet2!E7*100</f>
+        <f>Sheet2!E7*1000</f>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>Sheet2!F7*100</f>
+        <f>Sheet2!F7*1000</f>
         <v>0</v>
       </c>
       <c r="G7">
-        <f>Sheet2!G7*100</f>
+        <f>Sheet2!G7*1000</f>
         <v>0</v>
       </c>
       <c r="H7">
-        <f>Sheet2!H7*100</f>
+        <f>Sheet2!H7*1000</f>
         <v>0</v>
       </c>
       <c r="I7">
-        <f>Sheet2!I7*100</f>
+        <f>Sheet2!I7*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -2000,36 +2066,36 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <f>Sheet2!B8*100</f>
-        <v>5192.1291000000001</v>
+        <f>Sheet2!B8*1000</f>
+        <v>52518.400000000001</v>
       </c>
       <c r="C8">
-        <f>Sheet2!C8*100</f>
-        <v>-8852.5870999999988</v>
+        <f>Sheet2!C8*1000</f>
+        <v>-68492.7</v>
       </c>
       <c r="D8">
-        <f>Sheet2!D8*100</f>
-        <v>-10242.0731</v>
+        <f>Sheet2!D8*1000</f>
+        <v>-131398.30000000002</v>
       </c>
       <c r="E8">
-        <f>Sheet2!E8*100</f>
-        <v>-107.59460000000001</v>
+        <f>Sheet2!E8*1000</f>
+        <v>-4690.4000000000005</v>
       </c>
       <c r="F8">
-        <f>Sheet2!F8*100</f>
-        <v>-33204.049700000003</v>
+        <f>Sheet2!F8*1000</f>
+        <v>-434223.4</v>
       </c>
       <c r="G8">
-        <f>Sheet2!G8*100</f>
-        <v>4056.5762</v>
+        <f>Sheet2!G8*1000</f>
+        <v>30169.5</v>
       </c>
       <c r="H8">
-        <f>Sheet2!H8*100</f>
-        <v>-123.27550000000001</v>
+        <f>Sheet2!H8*1000</f>
+        <v>-1052.8999999999999</v>
       </c>
       <c r="I8">
-        <f>Sheet2!I8*100</f>
-        <v>216.27010000000001</v>
+        <f>Sheet2!I8*1000</f>
+        <v>283.89999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -2037,36 +2103,36 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <f>Sheet2!B9*100</f>
-        <v>61.266799999999996</v>
+        <f>Sheet2!B9*1000</f>
+        <v>-106.1</v>
       </c>
       <c r="C9">
-        <f>Sheet2!C9*100</f>
-        <v>1.7031999999999998</v>
+        <f>Sheet2!C9*1000</f>
+        <v>-9.7999999999999989</v>
       </c>
       <c r="D9">
-        <f>Sheet2!D9*100</f>
-        <v>565.4366</v>
+        <f>Sheet2!D9*1000</f>
+        <v>-703.8</v>
       </c>
       <c r="E9">
-        <f>Sheet2!E9*100</f>
-        <v>632.72299999999996</v>
+        <f>Sheet2!E9*1000</f>
+        <v>-40.300000000000004</v>
       </c>
       <c r="F9">
-        <f>Sheet2!F9*100</f>
-        <v>-46.7241</v>
+        <f>Sheet2!F9*1000</f>
+        <v>-109.5</v>
       </c>
       <c r="G9">
-        <f>Sheet2!G9*100</f>
-        <v>270.11250000000001</v>
+        <f>Sheet2!G9*1000</f>
+        <v>974.30000000000007</v>
       </c>
       <c r="H9">
-        <f>Sheet2!H9*100</f>
-        <v>-2.1768000000000001</v>
+        <f>Sheet2!H9*1000</f>
+        <v>-12.1</v>
       </c>
       <c r="I9">
-        <f>Sheet2!I9*100</f>
-        <v>-1076.1381000000001</v>
+        <f>Sheet2!I9*1000</f>
+        <v>44.3</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -2074,36 +2140,36 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <f>Sheet2!B10*100</f>
-        <v>0.4194</v>
+        <f>Sheet2!B10*1000</f>
+        <v>1.8</v>
       </c>
       <c r="C10">
-        <f>Sheet2!C10*100</f>
-        <v>1.3182</v>
+        <f>Sheet2!C10*1000</f>
+        <v>14.4</v>
       </c>
       <c r="D10">
-        <f>Sheet2!D10*100</f>
-        <v>1.1394</v>
+        <f>Sheet2!D10*1000</f>
+        <v>6.4</v>
       </c>
       <c r="E10">
-        <f>Sheet2!E10*100</f>
-        <v>26.932200000000002</v>
+        <f>Sheet2!E10*1000</f>
+        <v>326.40000000000003</v>
       </c>
       <c r="F10">
-        <f>Sheet2!F10*100</f>
-        <v>-0.3528</v>
+        <f>Sheet2!F10*1000</f>
+        <v>-25.5</v>
       </c>
       <c r="G10">
-        <f>Sheet2!G10*100</f>
-        <v>18.691199999999998</v>
+        <f>Sheet2!G10*1000</f>
+        <v>308.2</v>
       </c>
       <c r="H10">
-        <f>Sheet2!H10*100</f>
-        <v>-2.5724</v>
+        <f>Sheet2!H10*1000</f>
+        <v>-77</v>
       </c>
       <c r="I10">
-        <f>Sheet2!I10*100</f>
-        <v>-39.591000000000001</v>
+        <f>Sheet2!I10*1000</f>
+        <v>-349.7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -2111,35 +2177,35 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <f>Sheet2!B11*100</f>
+        <f>Sheet2!B11*1000</f>
         <v>0</v>
       </c>
       <c r="C11">
-        <f>Sheet2!C11*100</f>
+        <f>Sheet2!C11*1000</f>
         <v>0</v>
       </c>
       <c r="D11">
-        <f>Sheet2!D11*100</f>
+        <f>Sheet2!D11*1000</f>
         <v>0</v>
       </c>
       <c r="E11">
-        <f>Sheet2!E11*100</f>
+        <f>Sheet2!E11*1000</f>
         <v>0</v>
       </c>
       <c r="F11">
-        <f>Sheet2!F11*100</f>
+        <f>Sheet2!F11*1000</f>
         <v>0</v>
       </c>
       <c r="G11">
-        <f>Sheet2!G11*100</f>
+        <f>Sheet2!G11*1000</f>
         <v>0</v>
       </c>
       <c r="H11">
-        <f>Sheet2!H11*100</f>
+        <f>Sheet2!H11*1000</f>
         <v>0</v>
       </c>
       <c r="I11">
-        <f>Sheet2!I11*100</f>
+        <f>Sheet2!I11*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -2148,35 +2214,35 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <f>Sheet2!B12*100</f>
+        <f>Sheet2!B12*1000</f>
         <v>0</v>
       </c>
       <c r="C12">
-        <f>Sheet2!C12*100</f>
+        <f>Sheet2!C12*1000</f>
         <v>0</v>
       </c>
       <c r="D12">
-        <f>Sheet2!D12*100</f>
+        <f>Sheet2!D12*1000</f>
         <v>0</v>
       </c>
       <c r="E12">
-        <f>Sheet2!E12*100</f>
+        <f>Sheet2!E12*1000</f>
         <v>0</v>
       </c>
       <c r="F12">
-        <f>Sheet2!F12*100</f>
+        <f>Sheet2!F12*1000</f>
         <v>0</v>
       </c>
       <c r="G12">
-        <f>Sheet2!G12*100</f>
+        <f>Sheet2!G12*1000</f>
         <v>0</v>
       </c>
       <c r="H12">
-        <f>Sheet2!H12*100</f>
+        <f>Sheet2!H12*1000</f>
         <v>0</v>
       </c>
       <c r="I12">
-        <f>Sheet2!I12*100</f>
+        <f>Sheet2!I12*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -2185,35 +2251,35 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <f>Sheet2!B13*100</f>
+        <f>Sheet2!B13*1000</f>
         <v>0</v>
       </c>
       <c r="C13">
-        <f>Sheet2!C13*100</f>
+        <f>Sheet2!C13*1000</f>
         <v>0</v>
       </c>
       <c r="D13">
-        <f>Sheet2!D13*100</f>
+        <f>Sheet2!D13*1000</f>
         <v>0</v>
       </c>
       <c r="E13">
-        <f>Sheet2!E13*100</f>
+        <f>Sheet2!E13*1000</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>Sheet2!F13*100</f>
+        <f>Sheet2!F13*1000</f>
         <v>0</v>
       </c>
       <c r="G13">
-        <f>Sheet2!G13*100</f>
+        <f>Sheet2!G13*1000</f>
         <v>0</v>
       </c>
       <c r="H13">
-        <f>Sheet2!H13*100</f>
+        <f>Sheet2!H13*1000</f>
         <v>0</v>
       </c>
       <c r="I13">
-        <f>Sheet2!I13*100</f>
+        <f>Sheet2!I13*1000</f>
         <v>0</v>
       </c>
     </row>
@@ -2222,36 +2288,36 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <f>Sheet2!B14*100</f>
-        <v>-3019.9594000000002</v>
+        <f>Sheet2!B14*1000</f>
+        <v>-34202.800000000003</v>
       </c>
       <c r="C14">
-        <f>Sheet2!C14*100</f>
-        <v>-2364.3054999999999</v>
+        <f>Sheet2!C14*1000</f>
+        <v>-29851.600000000002</v>
       </c>
       <c r="D14">
-        <f>Sheet2!D14*100</f>
-        <v>-8711.7577000000001</v>
+        <f>Sheet2!D14*1000</f>
+        <v>-145708.5</v>
       </c>
       <c r="E14">
-        <f>Sheet2!E14*100</f>
-        <v>-1943.6703000000002</v>
+        <f>Sheet2!E14*1000</f>
+        <v>-23355.1</v>
       </c>
       <c r="F14">
-        <f>Sheet2!F14*100</f>
-        <v>-15339.0625</v>
+        <f>Sheet2!F14*1000</f>
+        <v>-265975.5</v>
       </c>
       <c r="G14">
-        <f>Sheet2!G14*100</f>
-        <v>-26566.311600000001</v>
+        <f>Sheet2!G14*1000</f>
+        <v>-306798</v>
       </c>
       <c r="H14">
-        <f>Sheet2!H14*100</f>
-        <v>-514.19470000000001</v>
+        <f>Sheet2!H14*1000</f>
+        <v>-7497.2000000000007</v>
       </c>
       <c r="I14">
-        <f>Sheet2!I14*100</f>
-        <v>-1114.1334000000002</v>
+        <f>Sheet2!I14*1000</f>
+        <v>-14496.6</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -2259,36 +2325,36 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <f>Sheet2!B15*100</f>
-        <v>208.77680000000001</v>
+        <f>Sheet2!B15*1000</f>
+        <v>-8918.9000000000015</v>
       </c>
       <c r="C15">
-        <f>Sheet2!C15*100</f>
-        <v>-467.64849999999996</v>
+        <f>Sheet2!C15*1000</f>
+        <v>-3666.9</v>
       </c>
       <c r="D15">
-        <f>Sheet2!D15*100</f>
-        <v>-20432.7454</v>
+        <f>Sheet2!D15*1000</f>
+        <v>-250579.7</v>
       </c>
       <c r="E15">
-        <f>Sheet2!E15*100</f>
-        <v>-742.82320000000004</v>
+        <f>Sheet2!E15*1000</f>
+        <v>-5807.7</v>
       </c>
       <c r="F15">
-        <f>Sheet2!F15*100</f>
-        <v>-73312.066699999996</v>
+        <f>Sheet2!F15*1000</f>
+        <v>-781123.5</v>
       </c>
       <c r="G15">
-        <f>Sheet2!G15*100</f>
-        <v>44667.910799999998</v>
+        <f>Sheet2!G15*1000</f>
+        <v>428169.2</v>
       </c>
       <c r="H15">
-        <f>Sheet2!H15*100</f>
-        <v>-5139.9303</v>
+        <f>Sheet2!H15*1000</f>
+        <v>-60349</v>
       </c>
       <c r="I15">
-        <f>Sheet2!I15*100</f>
-        <v>217.82119999999998</v>
+        <f>Sheet2!I15*1000</f>
+        <v>4809</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -2296,36 +2362,36 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <f>Sheet2!B16*100</f>
-        <v>2650.8166999999999</v>
+        <f>Sheet2!B16*1000</f>
+        <v>-19518.100000000002</v>
       </c>
       <c r="C16">
-        <f>Sheet2!C16*100</f>
-        <v>-27.185700000000001</v>
+        <f>Sheet2!C16*1000</f>
+        <v>-184.70000000000002</v>
       </c>
       <c r="D16">
-        <f>Sheet2!D16*100</f>
-        <v>-3158.6705999999999</v>
+        <f>Sheet2!D16*1000</f>
+        <v>-15155.099999999999</v>
       </c>
       <c r="E16">
-        <f>Sheet2!E16*100</f>
-        <v>-250.55600000000001</v>
+        <f>Sheet2!E16*1000</f>
+        <v>1962.5</v>
       </c>
       <c r="F16">
-        <f>Sheet2!F16*100</f>
-        <v>-4828.3478000000005</v>
+        <f>Sheet2!F16*1000</f>
+        <v>-62606.8</v>
       </c>
       <c r="G16">
-        <f>Sheet2!G16*100</f>
-        <v>6258.4885000000004</v>
+        <f>Sheet2!G16*1000</f>
+        <v>132868.5</v>
       </c>
       <c r="H16">
-        <f>Sheet2!H16*100</f>
-        <v>-1188.4573</v>
+        <f>Sheet2!H16*1000</f>
+        <v>-12829.4</v>
       </c>
       <c r="I16">
-        <f>Sheet2!I16*100</f>
-        <v>33.964800000000004</v>
+        <f>Sheet2!I16*1000</f>
+        <v>714.9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -2333,36 +2399,36 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <f>Sheet2!B17*100</f>
-        <v>54.722000000000001</v>
+        <f>Sheet2!B17*1000</f>
+        <v>-3703.1</v>
       </c>
       <c r="C17">
-        <f>Sheet2!C17*100</f>
-        <v>-0.36250000000000004</v>
+        <f>Sheet2!C17*1000</f>
+        <v>-5.4</v>
       </c>
       <c r="D17">
-        <f>Sheet2!D17*100</f>
-        <v>-148.55840000000001</v>
+        <f>Sheet2!D17*1000</f>
+        <v>-1804.6</v>
       </c>
       <c r="E17">
-        <f>Sheet2!E17*100</f>
-        <v>-98.438800000000001</v>
+        <f>Sheet2!E17*1000</f>
+        <v>-918.90000000000009</v>
       </c>
       <c r="F17">
-        <f>Sheet2!F17*100</f>
-        <v>-52.605500000000006</v>
+        <f>Sheet2!F17*1000</f>
+        <v>-692.30000000000007</v>
       </c>
       <c r="G17">
-        <f>Sheet2!G17*100</f>
-        <v>465.15690000000001</v>
+        <f>Sheet2!G17*1000</f>
+        <v>8980.4</v>
       </c>
       <c r="H17">
-        <f>Sheet2!H17*100</f>
-        <v>-209.23020000000002</v>
+        <f>Sheet2!H17*1000</f>
+        <v>-1687.2</v>
       </c>
       <c r="I17">
-        <f>Sheet2!I17*100</f>
-        <v>0.14499999999999999</v>
+        <f>Sheet2!I17*1000</f>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -2370,36 +2436,36 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <f>Sheet2!B18*100</f>
-        <v>8.8683999999999994</v>
+        <f>Sheet2!B18*1000</f>
+        <v>477.8</v>
       </c>
       <c r="C18">
-        <f>Sheet2!C18*100</f>
-        <v>0</v>
+        <f>Sheet2!C18*1000</f>
+        <v>303.3</v>
       </c>
       <c r="D18">
-        <f>Sheet2!D18*100</f>
-        <v>-29.504399999999997</v>
+        <f>Sheet2!D18*1000</f>
+        <v>25370.899999999998</v>
       </c>
       <c r="E18">
-        <f>Sheet2!E18*100</f>
-        <v>273.04270000000002</v>
+        <f>Sheet2!E18*1000</f>
+        <v>55158.6</v>
       </c>
       <c r="F18">
-        <f>Sheet2!F18*100</f>
-        <v>-27.462399999999999</v>
+        <f>Sheet2!F18*1000</f>
+        <v>-1488.6999999999998</v>
       </c>
       <c r="G18">
-        <f>Sheet2!G18*100</f>
-        <v>60.1967</v>
+        <f>Sheet2!G18*1000</f>
+        <v>6690.1</v>
       </c>
       <c r="H18">
-        <f>Sheet2!H18*100</f>
-        <v>-22.628499999999999</v>
+        <f>Sheet2!H18*1000</f>
+        <v>-4965.7</v>
       </c>
       <c r="I18">
-        <f>Sheet2!I18*100</f>
-        <v>-1.37E-2</v>
+        <f>Sheet2!I18*1000</f>
+        <v>-174.4</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -2407,36 +2473,36 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <f>Sheet2!B19*100</f>
-        <v>0</v>
+        <f>Sheet2!B19*1000</f>
+        <v>18.100000000000001</v>
       </c>
       <c r="C19">
-        <f>Sheet2!C19*100</f>
+        <f>Sheet2!C19*1000</f>
         <v>0</v>
       </c>
       <c r="D19">
-        <f>Sheet2!D19*100</f>
-        <v>0</v>
+        <f>Sheet2!D19*1000</f>
+        <v>562.6</v>
       </c>
       <c r="E19">
-        <f>Sheet2!E19*100</f>
-        <v>0</v>
+        <f>Sheet2!E19*1000</f>
+        <v>2526.6999999999998</v>
       </c>
       <c r="F19">
-        <f>Sheet2!F19*100</f>
-        <v>0</v>
+        <f>Sheet2!F19*1000</f>
+        <v>-77.399999999999991</v>
       </c>
       <c r="G19">
-        <f>Sheet2!G19*100</f>
-        <v>0</v>
+        <f>Sheet2!G19*1000</f>
+        <v>2861.4</v>
       </c>
       <c r="H19">
-        <f>Sheet2!H19*100</f>
-        <v>0</v>
+        <f>Sheet2!H19*1000</f>
+        <v>-498</v>
       </c>
       <c r="I19">
-        <f>Sheet2!I19*100</f>
-        <v>0</v>
+        <f>Sheet2!I19*1000</f>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -2480,7 +2546,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2489,10 +2555,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2506,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2515,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2532,7 +2598,7 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2541,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2558,7 +2624,7 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2567,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2584,7 +2650,7 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2593,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2610,7 +2676,7 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2619,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2636,7 +2702,7 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>10.3</v>
+        <v>12.888299999999999</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2645,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-2.75</v>
+        <v>-4.6871</v>
       </c>
       <c r="F8">
-        <v>-1.73</v>
+        <v>-0.65400000000000003</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2662,7 +2728,7 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2671,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.61399999999999999</v>
+        <v>4.6199999999999998E-2</v>
       </c>
       <c r="F9">
-        <v>-0.252</v>
+        <v>-2.3599999999999999E-2</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2688,7 +2754,7 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>-39.011200000000002</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2697,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.41299999999999998</v>
+        <v>14.817399999999999</v>
       </c>
       <c r="F10">
-        <v>-0.308</v>
+        <v>-47.356000000000002</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2714,7 +2780,7 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2723,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2740,7 +2806,7 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2749,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2766,7 +2832,7 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>9.31</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2775,10 +2841,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.97199999999999998</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>-7.62</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2792,7 +2858,7 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>2.12</v>
+        <v>2.5829</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2801,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-6.04</v>
+        <v>-5.4347000000000003</v>
       </c>
       <c r="F14">
-        <v>-6.34</v>
+        <v>-5.9673999999999996</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2818,7 +2884,7 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>8.8000000000000007</v>
+        <v>8.1611999999999991</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2827,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-2.38</v>
+        <v>-3.4195000000000002</v>
       </c>
       <c r="F15">
-        <v>-2.84</v>
+        <v>-2.9548000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2844,7 +2910,7 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>9.82</v>
+        <v>9.5708000000000002</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2853,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-5.7000000000000002E-2</v>
+        <v>0.22850000000000001</v>
       </c>
       <c r="F16">
-        <v>-3.19</v>
+        <v>-1.9999</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2870,7 +2936,7 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>9.74</v>
+        <v>3.3E-3</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2879,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>3.0000000000000001E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="F17">
-        <v>-2E-3</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2896,7 +2962,7 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>15.3</v>
+        <v>-2.7429999999999999</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2905,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.95</v>
+        <v>24.2072</v>
       </c>
       <c r="F18">
-        <v>-0.75900000000000001</v>
+        <v>-13.5535</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2922,7 +2988,7 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>9.31</v>
+        <v>7.2431000000000001</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2931,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.97199999999999998</v>
+        <v>7.1069000000000004</v>
       </c>
       <c r="F19">
-        <v>-7.62</v>
+        <v>-4.1295999999999999</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2950,10 +3016,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79204781-DFD6-42BD-B3F6-FA59E37126C4}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2982,7 +3048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3011,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3040,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3069,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3098,7 +3164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3127,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3156,12 +3222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <v>756</v>
+        <v>654.81020000000001</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -3170,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-431</v>
+        <v>-556.88630000000001</v>
       </c>
       <c r="F8">
-        <v>-325</v>
+        <v>-97.924400000000006</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3185,7 +3251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3199,10 +3265,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>4.0599999999999996</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="F9">
-        <v>-4.0599999999999996</v>
+        <v>-3.6999999999999998E-2</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3213,8 +3279,32 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3228,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.06</v>
+        <v>0.2051</v>
       </c>
       <c r="F10">
-        <v>-0.06</v>
+        <v>-0.2051</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3242,8 +3332,32 @@
       <c r="I10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>5.3948999999999998</v>
+      </c>
+      <c r="R10">
+        <v>-5.3948999999999998</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3271,8 +3385,32 @@
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>81.371899999999997</v>
+      </c>
+      <c r="R11">
+        <v>-81.371899999999997</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3300,8 +3438,32 @@
       <c r="I12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0.17319999999999999</v>
+      </c>
+      <c r="R12">
+        <v>-0.17319999999999999</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3329,13 +3491,37 @@
       <c r="I13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M13" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13">
+        <v>715.55430000000001</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>25.251899999999999</v>
+      </c>
+      <c r="R13">
+        <v>-740.80600000000004</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14">
-        <v>2153</v>
+        <v>2714.4097000000002</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3344,10 +3530,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-596</v>
+        <v>-827.8854</v>
       </c>
       <c r="F14">
-        <v>-1557</v>
+        <v>-1886.5245</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3358,13 +3544,37 @@
       <c r="I14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M14" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14">
+        <v>2908.5659000000001</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>-677.46699999999998</v>
+      </c>
+      <c r="R14">
+        <v>-2231.0979000000002</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>3399</v>
+        <v>2908.5659000000001</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3373,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-550</v>
+        <v>-677.46699999999998</v>
       </c>
       <c r="F15">
-        <v>-2849</v>
+        <v>-2231.0979000000002</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3387,13 +3597,37 @@
       <c r="I15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M15" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15">
+        <v>2714.4097000000002</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>-827.8854</v>
+      </c>
+      <c r="R15">
+        <v>-1886.5245</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
       <c r="B16">
-        <v>608</v>
+        <v>715.55430000000001</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -3402,10 +3636,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-5.0999999999999996</v>
+        <v>25.251899999999999</v>
       </c>
       <c r="F16">
-        <v>-603</v>
+        <v>-740.80600000000004</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3416,8 +3650,32 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M16" t="s">
+        <v>45</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3431,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.108</v>
+        <v>0.17319999999999999</v>
       </c>
       <c r="F17">
-        <v>-0.108</v>
+        <v>-0.17319999999999999</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3445,8 +3703,32 @@
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M17" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3460,10 +3742,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>2.62</v>
+        <v>81.371899999999997</v>
       </c>
       <c r="F18">
-        <v>-2.62</v>
+        <v>-81.371899999999997</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3474,8 +3756,32 @@
       <c r="I18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3489,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>5.3948999999999998</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>-5.3948999999999998</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3503,8 +3809,32 @@
       <c r="I19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M19" t="s">
+        <v>48</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0.2051</v>
+      </c>
+      <c r="R19">
+        <v>-0.2051</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3530,6 +3860,212 @@
         <v>0</v>
       </c>
       <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>49</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="R20">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21">
+        <v>654.81020000000001</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>-556.88630000000001</v>
+      </c>
+      <c r="R21">
+        <v>-97.924400000000006</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M22" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M23" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M24" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M26" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M27" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
         <v>0</v>
       </c>
     </row>
@@ -3612,7 +4148,7 @@
       </c>
       <c r="B8">
         <f>Sheet5!F8*1000</f>
-        <v>-325000</v>
+        <v>-97924.400000000009</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -3621,7 +4157,7 @@
       </c>
       <c r="B9">
         <f>Sheet5!F9*1000</f>
-        <v>-4059.9999999999995</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -3630,7 +4166,7 @@
       </c>
       <c r="B10">
         <f>Sheet5!F10*1000</f>
-        <v>-60</v>
+        <v>-205.1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -3666,7 +4202,7 @@
       </c>
       <c r="B14">
         <f>Sheet5!F14*1000</f>
-        <v>-1557000</v>
+        <v>-1886524.5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -3675,7 +4211,7 @@
       </c>
       <c r="B15">
         <f>Sheet5!F15*1000</f>
-        <v>-2849000</v>
+        <v>-2231097.9000000004</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -3684,7 +4220,7 @@
       </c>
       <c r="B16">
         <f>Sheet5!F16*1000</f>
-        <v>-603000</v>
+        <v>-740806</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -3693,7 +4229,7 @@
       </c>
       <c r="B17">
         <f>Sheet5!F17*1000</f>
-        <v>-108</v>
+        <v>-173.2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -3702,7 +4238,7 @@
       </c>
       <c r="B18">
         <f>Sheet5!F18*1000</f>
-        <v>-2620</v>
+        <v>-81371.899999999994</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -3711,7 +4247,7 @@
       </c>
       <c r="B19">
         <f>Sheet5!F19*1000</f>
-        <v>0</v>
+        <v>-5394.9</v>
       </c>
     </row>
   </sheetData>
@@ -3792,7 +4328,7 @@
       </c>
       <c r="B8">
         <f>Sheet5!B8*1000</f>
-        <v>756000</v>
+        <v>654810.19999999995</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -3846,7 +4382,7 @@
       </c>
       <c r="B14">
         <f>Sheet5!B14*1000</f>
-        <v>2153000</v>
+        <v>2714409.7</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -3855,7 +4391,7 @@
       </c>
       <c r="B15">
         <f>Sheet5!B15*1000</f>
-        <v>3399000</v>
+        <v>2908565.9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -3864,7 +4400,7 @@
       </c>
       <c r="B16">
         <f>Sheet5!B16*1000</f>
-        <v>608000</v>
+        <v>715554.3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
